--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.00285954044548</v>
+        <v>9.750464675322391</v>
       </c>
       <c r="D2" t="n">
-        <v>60.26493749727386</v>
+        <v>9.793052343307004</v>
       </c>
       <c r="E2" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F2" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.17430059404097</v>
+        <v>2.628323846531658</v>
       </c>
       <c r="D3" t="n">
-        <v>15.94017563771603</v>
+        <v>2.590278541128855</v>
       </c>
       <c r="E3" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F3" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.3006207781356</v>
+        <v>1.673850876447035</v>
       </c>
       <c r="D4" t="n">
-        <v>10.40157629706438</v>
+        <v>1.690256148272961</v>
       </c>
       <c r="E4" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F4" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.35534559350225</v>
+        <v>2.332743658944116</v>
       </c>
       <c r="D5" t="n">
-        <v>14.17036706253569</v>
+        <v>2.30268464766205</v>
       </c>
       <c r="E5" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F5" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.23568300571777</v>
+        <v>8.163298488429138</v>
       </c>
       <c r="D6" t="n">
-        <v>50.80191458699449</v>
+        <v>8.255311120386605</v>
       </c>
       <c r="E6" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F6" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.75525766829477</v>
+        <v>4.672729371097901</v>
       </c>
       <c r="D7" t="n">
-        <v>29.30390191305464</v>
+        <v>4.761884060871378</v>
       </c>
       <c r="E7" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F7" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.1198027520198</v>
+        <v>9.119467947203217</v>
       </c>
       <c r="D8" t="n">
-        <v>55.61490891316207</v>
+        <v>9.037422698388836</v>
       </c>
       <c r="E8" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F8" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.47245927745031</v>
+        <v>3.651774632585675</v>
       </c>
       <c r="D9" t="n">
-        <v>22.68432256651522</v>
+        <v>3.686202417058723</v>
       </c>
       <c r="E9" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F9" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.66446598778156</v>
+        <v>4.982975723014504</v>
       </c>
       <c r="D10" t="n">
-        <v>30.34076681419068</v>
+        <v>4.930374607305986</v>
       </c>
       <c r="E10" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F10" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.28612126334149</v>
+        <v>4.108994705292993</v>
       </c>
       <c r="D11" t="n">
-        <v>25.30647269898744</v>
+        <v>4.112301813585459</v>
       </c>
       <c r="E11" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F11" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.6581987997353</v>
+        <v>4.494457304956986</v>
       </c>
       <c r="D12" t="n">
-        <v>27.48636835979352</v>
+        <v>4.466534858466447</v>
       </c>
       <c r="E12" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F12" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.13126521162988</v>
+        <v>7.821330596889856</v>
       </c>
       <c r="D13" t="n">
-        <v>48.22736523508901</v>
+        <v>7.836946850701964</v>
       </c>
       <c r="E13" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F13" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89169194112327</v>
+        <v>3.394899940432531</v>
       </c>
       <c r="D14" t="n">
-        <v>20.69684401984318</v>
+        <v>3.363237153224517</v>
       </c>
       <c r="E14" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F14" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>26.09542822385714</v>
+        <v>4.240507086376786</v>
       </c>
       <c r="D15" t="n">
-        <v>25.97109432914057</v>
+        <v>4.220302828485344</v>
       </c>
       <c r="E15" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F15" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>24.00211116678559</v>
+        <v>3.900343064602659</v>
       </c>
       <c r="D16" t="n">
-        <v>23.94485446844617</v>
+        <v>3.891038851122503</v>
       </c>
       <c r="E16" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F16" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>7.394563675889885</v>
+        <v>1.201616597332106</v>
       </c>
       <c r="D17" t="n">
-        <v>7.272766988855402</v>
+        <v>1.181824635689003</v>
       </c>
       <c r="E17" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F17" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>40.96593320147731</v>
+        <v>6.656964145240064</v>
       </c>
       <c r="D18" t="n">
-        <v>41.02620017885008</v>
+        <v>6.666757529063138</v>
       </c>
       <c r="E18" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F18" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>43.79482376425781</v>
+        <v>7.116658861691894</v>
       </c>
       <c r="D19" t="n">
-        <v>43.95005151636878</v>
+        <v>7.141883371409927</v>
       </c>
       <c r="E19" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F19" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>8.937570781481631</v>
+        <v>1.452355251990765</v>
       </c>
       <c r="D20" t="n">
-        <v>9.093434232266633</v>
+        <v>1.477683062743328</v>
       </c>
       <c r="E20" t="n">
-        <v>15.60560472610897</v>
+        <v>2.535910767992707</v>
       </c>
       <c r="F20" t="n">
-        <v>15.65776143326682</v>
+        <v>2.544386232905859</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
